--- a/dye_list.xlsx
+++ b/dye_list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3F11\Desktop\암호화파일 만들기\real data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3F11\Desktop\XML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3060C302-8FE7-46E0-B525-1796976F057E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA2731E-4688-4C1C-AEC9-73856BEDB642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="183">
   <si>
     <t>Suncion Yellow H-E4G</t>
   </si>
@@ -500,42 +500,6 @@
   </si>
   <si>
     <t>Sunzol Black CP-R</t>
-  </si>
-  <si>
-    <t>Daenong</t>
-  </si>
-  <si>
-    <t>Birkim</t>
-  </si>
-  <si>
-    <t>Alrowad</t>
-  </si>
-  <si>
-    <t>UFS</t>
-  </si>
-  <si>
-    <t>P.P. COLOUR</t>
-  </si>
-  <si>
-    <t>Win Textile</t>
-  </si>
-  <si>
-    <t>Quimtia</t>
-  </si>
-  <si>
-    <t>영덕물산</t>
-  </si>
-  <si>
-    <t>일신방직</t>
-  </si>
-  <si>
-    <t>Texco Tech</t>
-  </si>
-  <si>
-    <t>Nivas Colors 인도</t>
-  </si>
-  <si>
-    <t>Nivas Colors 스리랑카</t>
   </si>
   <si>
     <t>Sunfix Red SBS 150%</t>
@@ -547,6 +511,81 @@
   </si>
   <si>
     <t>Sunfix Stay Navy Blue HP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfix HP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncion H-E</t>
+  </si>
+  <si>
+    <t>Suncion H-EL</t>
+  </si>
+  <si>
+    <t>Sunfix SPR</t>
+  </si>
+  <si>
+    <t>Sunfix SPD conc.</t>
+  </si>
+  <si>
+    <t>Sunfix EX</t>
+  </si>
+  <si>
+    <t>Sunfix SS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfron SN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfix MF-D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfix Classic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunzol Classic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfron C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncion Yellow CP-R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunzol GRB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunfix FE-A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunzol Black</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncion CP-R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncion Orange CP-R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncion Deep Red CP-R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suncion Brown CP-R</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -896,13 +935,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O151"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="31.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1</v>
       </c>
@@ -912,11 +952,11 @@
       <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -926,26 +966,11 @@
       <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="D2" t="s">
         <v>164</v>
       </c>
-      <c r="J2" t="s">
-        <v>166</v>
-      </c>
-      <c r="M2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -955,118 +980,109 @@
       <c r="C3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>5</v>
       </c>
-      <c r="E6" t="s">
-        <v>161</v>
-      </c>
-      <c r="G6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>161</v>
-      </c>
-      <c r="J8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>161</v>
-      </c>
-      <c r="F9" t="s">
-        <v>162</v>
-      </c>
-      <c r="G9" t="s">
-        <v>163</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1076,104 +1092,92 @@
       <c r="C11" t="s">
         <v>10</v>
       </c>
-      <c r="E11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>161</v>
-      </c>
-      <c r="F12" t="s">
-        <v>162</v>
-      </c>
-      <c r="J12" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>5</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" t="s">
-        <v>161</v>
-      </c>
-      <c r="F13" t="s">
-        <v>162</v>
-      </c>
-      <c r="J13" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+      <c r="D13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
         <v>13</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C17" t="s">
         <v>13</v>
       </c>
-      <c r="E14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>6</v>
-      </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" t="s">
-        <v>161</v>
-      </c>
-      <c r="F15" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -1183,8 +1187,11 @@
       <c r="C18" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -1194,23 +1201,11 @@
       <c r="C19" t="s">
         <v>18</v>
       </c>
-      <c r="E19" t="s">
-        <v>161</v>
-      </c>
-      <c r="F19" t="s">
-        <v>162</v>
-      </c>
-      <c r="J19" t="s">
-        <v>166</v>
-      </c>
-      <c r="M19" t="s">
-        <v>169</v>
-      </c>
-      <c r="N19" t="s">
+      <c r="D19" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -1220,11 +1215,11 @@
       <c r="C20" t="s">
         <v>19</v>
       </c>
-      <c r="J20" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>3</v>
       </c>
@@ -1234,20 +1229,11 @@
       <c r="C21" t="s">
         <v>20</v>
       </c>
-      <c r="E21" t="s">
-        <v>161</v>
-      </c>
-      <c r="F21" t="s">
-        <v>162</v>
-      </c>
-      <c r="J21" t="s">
-        <v>166</v>
-      </c>
-      <c r="N21" t="s">
+      <c r="D21" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>3</v>
       </c>
@@ -1257,14 +1243,11 @@
       <c r="C22" t="s">
         <v>152</v>
       </c>
-      <c r="F22" t="s">
-        <v>162</v>
-      </c>
-      <c r="M22" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1274,8 +1257,11 @@
       <c r="C23" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1285,8 +1271,11 @@
       <c r="C24" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1296,8 +1285,11 @@
       <c r="C25" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>5</v>
       </c>
@@ -1307,32 +1299,11 @@
       <c r="C26" t="s">
         <v>24</v>
       </c>
-      <c r="E26" t="s">
-        <v>161</v>
-      </c>
-      <c r="F26" t="s">
-        <v>162</v>
-      </c>
-      <c r="I26" t="s">
-        <v>165</v>
-      </c>
-      <c r="J26" t="s">
-        <v>166</v>
-      </c>
-      <c r="K26" t="s">
-        <v>167</v>
-      </c>
-      <c r="L26" t="s">
-        <v>168</v>
-      </c>
-      <c r="M26" t="s">
-        <v>169</v>
-      </c>
-      <c r="N26" t="s">
+      <c r="D26" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>6</v>
       </c>
@@ -1342,14 +1313,11 @@
       <c r="C27" t="s">
         <v>25</v>
       </c>
-      <c r="E27" t="s">
-        <v>161</v>
-      </c>
-      <c r="N27" t="s">
+      <c r="D27" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>6</v>
       </c>
@@ -1359,8 +1327,11 @@
       <c r="C28" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1</v>
       </c>
@@ -1370,26 +1341,11 @@
       <c r="C29" t="s">
         <v>27</v>
       </c>
-      <c r="E29" t="s">
-        <v>161</v>
-      </c>
-      <c r="F29" t="s">
-        <v>162</v>
-      </c>
-      <c r="H29" t="s">
-        <v>164</v>
-      </c>
-      <c r="M29" t="s">
-        <v>169</v>
-      </c>
-      <c r="N29" t="s">
-        <v>170</v>
-      </c>
-      <c r="O29" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D29" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -1399,32 +1355,11 @@
       <c r="C30" t="s">
         <v>28</v>
       </c>
-      <c r="E30" t="s">
-        <v>161</v>
-      </c>
-      <c r="F30" t="s">
-        <v>162</v>
-      </c>
-      <c r="H30" t="s">
-        <v>164</v>
-      </c>
-      <c r="I30" t="s">
-        <v>165</v>
-      </c>
-      <c r="J30" t="s">
+      <c r="D30" t="s">
         <v>166</v>
       </c>
-      <c r="K30" t="s">
-        <v>167</v>
-      </c>
-      <c r="L30" t="s">
-        <v>168</v>
-      </c>
-      <c r="N30" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -1434,29 +1369,11 @@
       <c r="C31" t="s">
         <v>29</v>
       </c>
-      <c r="E31" t="s">
-        <v>161</v>
-      </c>
-      <c r="F31" t="s">
-        <v>162</v>
-      </c>
-      <c r="H31" t="s">
-        <v>164</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="D31" t="s">
         <v>166</v>
       </c>
-      <c r="M31" t="s">
-        <v>169</v>
-      </c>
-      <c r="N31" t="s">
-        <v>170</v>
-      </c>
-      <c r="O31" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>5</v>
       </c>
@@ -1467,31 +1384,10 @@
         <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>160</v>
-      </c>
-      <c r="E32" t="s">
-        <v>161</v>
-      </c>
-      <c r="F32" t="s">
-        <v>162</v>
-      </c>
-      <c r="G32" t="s">
-        <v>163</v>
-      </c>
-      <c r="H32" t="s">
-        <v>164</v>
-      </c>
-      <c r="J32" t="s">
         <v>166</v>
       </c>
-      <c r="M32" t="s">
-        <v>169</v>
-      </c>
-      <c r="O32" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>5</v>
       </c>
@@ -1501,23 +1397,11 @@
       <c r="C33" t="s">
         <v>31</v>
       </c>
-      <c r="F33" t="s">
-        <v>162</v>
-      </c>
-      <c r="H33" t="s">
-        <v>164</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="D33" t="s">
         <v>166</v>
       </c>
-      <c r="N33" t="s">
-        <v>170</v>
-      </c>
-      <c r="O33" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1</v>
       </c>
@@ -1527,32 +1411,11 @@
       <c r="C34" t="s">
         <v>32</v>
       </c>
-      <c r="E34" t="s">
-        <v>161</v>
-      </c>
-      <c r="F34" t="s">
-        <v>162</v>
-      </c>
-      <c r="G34" t="s">
-        <v>163</v>
-      </c>
-      <c r="H34" t="s">
-        <v>164</v>
-      </c>
-      <c r="J34" t="s">
-        <v>166</v>
-      </c>
-      <c r="M34" t="s">
-        <v>169</v>
-      </c>
-      <c r="N34" t="s">
-        <v>170</v>
-      </c>
-      <c r="O34" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -1562,35 +1425,11 @@
       <c r="C35" t="s">
         <v>33</v>
       </c>
-      <c r="E35" t="s">
-        <v>161</v>
-      </c>
-      <c r="F35" t="s">
-        <v>162</v>
-      </c>
-      <c r="G35" t="s">
-        <v>163</v>
-      </c>
-      <c r="H35" t="s">
-        <v>164</v>
-      </c>
-      <c r="I35" t="s">
-        <v>165</v>
-      </c>
-      <c r="J35" t="s">
-        <v>166</v>
-      </c>
-      <c r="M35" t="s">
-        <v>169</v>
-      </c>
-      <c r="N35" t="s">
-        <v>170</v>
-      </c>
-      <c r="O35" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D35" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>6</v>
       </c>
@@ -1600,23 +1439,11 @@
       <c r="C36" t="s">
         <v>34</v>
       </c>
-      <c r="E36" t="s">
-        <v>161</v>
-      </c>
-      <c r="F36" t="s">
-        <v>162</v>
-      </c>
-      <c r="H36" t="s">
-        <v>164</v>
-      </c>
-      <c r="M36" t="s">
-        <v>169</v>
-      </c>
-      <c r="N36" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D36" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>5</v>
       </c>
@@ -1626,23 +1453,11 @@
       <c r="C37" t="s">
         <v>153</v>
       </c>
-      <c r="E37" t="s">
-        <v>161</v>
-      </c>
-      <c r="F37" t="s">
-        <v>162</v>
-      </c>
-      <c r="H37" t="s">
-        <v>164</v>
-      </c>
-      <c r="M37" t="s">
-        <v>169</v>
-      </c>
-      <c r="O37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D37" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>6</v>
       </c>
@@ -1652,17 +1467,11 @@
       <c r="C38" t="s">
         <v>35</v>
       </c>
-      <c r="F38" t="s">
-        <v>162</v>
-      </c>
-      <c r="N38" t="s">
-        <v>170</v>
-      </c>
-      <c r="O38" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D38" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1</v>
       </c>
@@ -1672,23 +1481,11 @@
       <c r="C39" t="s">
         <v>36</v>
       </c>
-      <c r="F39" t="s">
-        <v>162</v>
-      </c>
-      <c r="H39" t="s">
-        <v>164</v>
-      </c>
-      <c r="M39" t="s">
-        <v>169</v>
-      </c>
-      <c r="N39" t="s">
-        <v>170</v>
-      </c>
-      <c r="O39" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D39" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -1698,20 +1495,11 @@
       <c r="C40" t="s">
         <v>37</v>
       </c>
-      <c r="F40" t="s">
-        <v>162</v>
-      </c>
-      <c r="H40" t="s">
-        <v>164</v>
-      </c>
-      <c r="M40" t="s">
-        <v>169</v>
-      </c>
-      <c r="N40" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>5</v>
       </c>
@@ -1721,20 +1509,11 @@
       <c r="C41" t="s">
         <v>38</v>
       </c>
-      <c r="F41" t="s">
-        <v>162</v>
-      </c>
-      <c r="H41" t="s">
-        <v>164</v>
-      </c>
-      <c r="J41" t="s">
-        <v>166</v>
-      </c>
-      <c r="M41" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D41" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>6</v>
       </c>
@@ -1744,11 +1523,11 @@
       <c r="C42" t="s">
         <v>39</v>
       </c>
-      <c r="N42" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D42" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>6</v>
       </c>
@@ -1758,14 +1537,11 @@
       <c r="C43" t="s">
         <v>40</v>
       </c>
-      <c r="M43" t="s">
-        <v>169</v>
-      </c>
-      <c r="N43" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D43" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1</v>
       </c>
@@ -1775,23 +1551,11 @@
       <c r="C44" t="s">
         <v>41</v>
       </c>
-      <c r="E44" t="s">
-        <v>161</v>
-      </c>
-      <c r="F44" t="s">
-        <v>162</v>
-      </c>
-      <c r="H44" t="s">
-        <v>164</v>
-      </c>
-      <c r="I44" t="s">
-        <v>165</v>
-      </c>
-      <c r="M44" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D44" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1</v>
       </c>
@@ -1801,26 +1565,11 @@
       <c r="C45" t="s">
         <v>42</v>
       </c>
-      <c r="E45" t="s">
-        <v>161</v>
-      </c>
-      <c r="F45" t="s">
-        <v>162</v>
-      </c>
-      <c r="G45" t="s">
+      <c r="D45" t="s">
         <v>163</v>
       </c>
-      <c r="H45" t="s">
-        <v>164</v>
-      </c>
-      <c r="M45" t="s">
-        <v>169</v>
-      </c>
-      <c r="N45" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1</v>
       </c>
@@ -1830,20 +1579,11 @@
       <c r="C46" t="s">
         <v>43</v>
       </c>
-      <c r="G46" t="s">
+      <c r="D46" t="s">
         <v>163</v>
       </c>
-      <c r="H46" t="s">
-        <v>164</v>
-      </c>
-      <c r="J46" t="s">
-        <v>166</v>
-      </c>
-      <c r="M46" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1</v>
       </c>
@@ -1853,26 +1593,11 @@
       <c r="C47" t="s">
         <v>44</v>
       </c>
-      <c r="F47" t="s">
-        <v>162</v>
-      </c>
-      <c r="H47" t="s">
-        <v>164</v>
-      </c>
-      <c r="J47" t="s">
-        <v>166</v>
-      </c>
-      <c r="M47" t="s">
-        <v>169</v>
-      </c>
-      <c r="N47" t="s">
-        <v>170</v>
-      </c>
-      <c r="O47" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D47" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2</v>
       </c>
@@ -1882,17 +1607,11 @@
       <c r="C48" t="s">
         <v>45</v>
       </c>
-      <c r="G48" t="s">
+      <c r="D48" t="s">
         <v>163</v>
       </c>
-      <c r="H48" t="s">
-        <v>164</v>
-      </c>
-      <c r="N48" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>3</v>
       </c>
@@ -1902,17 +1621,11 @@
       <c r="C49" t="s">
         <v>46</v>
       </c>
-      <c r="H49" t="s">
-        <v>164</v>
-      </c>
-      <c r="J49" t="s">
-        <v>166</v>
-      </c>
-      <c r="M49" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D49" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>3</v>
       </c>
@@ -1922,20 +1635,11 @@
       <c r="C50" t="s">
         <v>47</v>
       </c>
-      <c r="G50" t="s">
+      <c r="D50" t="s">
         <v>163</v>
       </c>
-      <c r="H50" t="s">
-        <v>164</v>
-      </c>
-      <c r="J50" t="s">
-        <v>166</v>
-      </c>
-      <c r="M50" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>3</v>
       </c>
@@ -1945,17 +1649,11 @@
       <c r="C51" t="s">
         <v>48</v>
       </c>
-      <c r="F51" t="s">
-        <v>162</v>
-      </c>
-      <c r="G51" t="s">
+      <c r="D51" t="s">
         <v>163</v>
       </c>
-      <c r="H51" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>5</v>
       </c>
@@ -1965,20 +1663,11 @@
       <c r="C52" t="s">
         <v>49</v>
       </c>
-      <c r="F52" t="s">
-        <v>162</v>
-      </c>
-      <c r="G52" t="s">
+      <c r="D52" t="s">
         <v>163</v>
       </c>
-      <c r="H52" t="s">
-        <v>164</v>
-      </c>
-      <c r="M52" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>6</v>
       </c>
@@ -1988,8 +1677,11 @@
       <c r="C53" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D53" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>6</v>
       </c>
@@ -1997,10 +1689,13 @@
         <v>51</v>
       </c>
       <c r="C54" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+      <c r="D54" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>6</v>
       </c>
@@ -2010,26 +1705,11 @@
       <c r="C55" t="s">
         <v>54</v>
       </c>
-      <c r="F55" t="s">
-        <v>162</v>
-      </c>
-      <c r="G55" t="s">
+      <c r="D55" t="s">
         <v>163</v>
       </c>
-      <c r="H55" t="s">
-        <v>164</v>
-      </c>
-      <c r="J55" t="s">
-        <v>166</v>
-      </c>
-      <c r="M55" t="s">
-        <v>169</v>
-      </c>
-      <c r="N55" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -2039,14 +1719,11 @@
       <c r="C56" t="s">
         <v>52</v>
       </c>
-      <c r="H56" t="s">
-        <v>164</v>
-      </c>
-      <c r="M56" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D56" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>6</v>
       </c>
@@ -2056,52 +1733,22 @@
       <c r="C57" t="s">
         <v>53</v>
       </c>
-      <c r="F57" t="s">
-        <v>162</v>
-      </c>
-      <c r="G57" t="s">
+      <c r="D57" t="s">
         <v>163</v>
       </c>
-      <c r="H57" t="s">
-        <v>164</v>
-      </c>
-      <c r="M57" t="s">
-        <v>169</v>
-      </c>
-      <c r="N57" t="s">
-        <v>170</v>
-      </c>
-      <c r="O57" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>55</v>
       </c>
       <c r="C58" t="s">
         <v>55</v>
       </c>
-      <c r="E58" t="s">
-        <v>161</v>
-      </c>
-      <c r="F58" t="s">
-        <v>162</v>
-      </c>
-      <c r="G58" t="s">
+      <c r="D58" t="s">
         <v>163</v>
       </c>
-      <c r="J58" t="s">
-        <v>166</v>
-      </c>
-      <c r="M58" t="s">
-        <v>169</v>
-      </c>
-      <c r="N58" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1</v>
       </c>
@@ -2111,14 +1758,11 @@
       <c r="C59" t="s">
         <v>56</v>
       </c>
-      <c r="I59" t="s">
-        <v>165</v>
-      </c>
-      <c r="M59" t="s">
+      <c r="D59" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1</v>
       </c>
@@ -2128,23 +1772,11 @@
       <c r="C60" t="s">
         <v>57</v>
       </c>
-      <c r="F60" t="s">
-        <v>162</v>
-      </c>
-      <c r="H60" t="s">
-        <v>164</v>
-      </c>
-      <c r="J60" t="s">
-        <v>166</v>
-      </c>
-      <c r="K60" t="s">
-        <v>167</v>
-      </c>
-      <c r="M60" t="s">
+      <c r="D60" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1</v>
       </c>
@@ -2154,29 +1786,11 @@
       <c r="C61" t="s">
         <v>58</v>
       </c>
-      <c r="F61" t="s">
-        <v>162</v>
-      </c>
-      <c r="G61" t="s">
-        <v>163</v>
-      </c>
-      <c r="H61" t="s">
-        <v>164</v>
-      </c>
-      <c r="J61" t="s">
-        <v>166</v>
-      </c>
-      <c r="M61" t="s">
+      <c r="D61" t="s">
         <v>169</v>
       </c>
-      <c r="N61" t="s">
-        <v>170</v>
-      </c>
-      <c r="O61" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>2</v>
       </c>
@@ -2186,29 +1800,11 @@
       <c r="C62" t="s">
         <v>59</v>
       </c>
-      <c r="E62" t="s">
-        <v>161</v>
-      </c>
-      <c r="F62" t="s">
-        <v>162</v>
-      </c>
-      <c r="G62" t="s">
-        <v>163</v>
-      </c>
-      <c r="H62" t="s">
-        <v>164</v>
-      </c>
-      <c r="J62" t="s">
-        <v>166</v>
-      </c>
-      <c r="M62" t="s">
+      <c r="D62" t="s">
         <v>169</v>
       </c>
-      <c r="N62" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>3</v>
       </c>
@@ -2218,20 +1814,11 @@
       <c r="C63" t="s">
         <v>60</v>
       </c>
-      <c r="E63" t="s">
-        <v>161</v>
-      </c>
-      <c r="H63" t="s">
-        <v>164</v>
-      </c>
-      <c r="I63" t="s">
-        <v>165</v>
-      </c>
-      <c r="J63" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D63" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>3</v>
       </c>
@@ -2241,17 +1828,11 @@
       <c r="C64" t="s">
         <v>61</v>
       </c>
-      <c r="F64" t="s">
-        <v>162</v>
-      </c>
-      <c r="H64" t="s">
-        <v>164</v>
-      </c>
-      <c r="M64" t="s">
+      <c r="D64" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>3</v>
       </c>
@@ -2261,26 +1842,11 @@
       <c r="C65" t="s">
         <v>62</v>
       </c>
-      <c r="F65" t="s">
-        <v>162</v>
-      </c>
-      <c r="H65" t="s">
-        <v>164</v>
-      </c>
-      <c r="J65" t="s">
-        <v>166</v>
-      </c>
-      <c r="M65" t="s">
+      <c r="D65" t="s">
         <v>169</v>
       </c>
-      <c r="N65" t="s">
-        <v>170</v>
-      </c>
-      <c r="O65" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>3</v>
       </c>
@@ -2290,29 +1856,11 @@
       <c r="C66" t="s">
         <v>63</v>
       </c>
-      <c r="E66" t="s">
-        <v>161</v>
-      </c>
-      <c r="F66" t="s">
-        <v>162</v>
-      </c>
-      <c r="H66" t="s">
-        <v>164</v>
-      </c>
-      <c r="J66" t="s">
-        <v>166</v>
-      </c>
-      <c r="M66" t="s">
+      <c r="D66" t="s">
         <v>169</v>
       </c>
-      <c r="N66" t="s">
-        <v>170</v>
-      </c>
-      <c r="O66" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>5</v>
       </c>
@@ -2322,38 +1870,11 @@
       <c r="C67" t="s">
         <v>64</v>
       </c>
-      <c r="E67" t="s">
-        <v>161</v>
-      </c>
-      <c r="F67" t="s">
-        <v>162</v>
-      </c>
-      <c r="G67" t="s">
-        <v>163</v>
-      </c>
-      <c r="H67" t="s">
-        <v>164</v>
-      </c>
-      <c r="I67" t="s">
-        <v>165</v>
-      </c>
-      <c r="J67" t="s">
-        <v>166</v>
-      </c>
-      <c r="K67" t="s">
-        <v>167</v>
-      </c>
-      <c r="L67" t="s">
-        <v>168</v>
-      </c>
-      <c r="M67" t="s">
+      <c r="D67" t="s">
         <v>169</v>
       </c>
-      <c r="N67" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>6</v>
       </c>
@@ -2363,23 +1884,11 @@
       <c r="C68" t="s">
         <v>65</v>
       </c>
-      <c r="F68" t="s">
-        <v>162</v>
-      </c>
-      <c r="H68" t="s">
-        <v>164</v>
-      </c>
-      <c r="I68" t="s">
-        <v>165</v>
-      </c>
-      <c r="J68" t="s">
-        <v>166</v>
-      </c>
-      <c r="M68" t="s">
+      <c r="D68" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>6</v>
       </c>
@@ -2389,29 +1898,11 @@
       <c r="C69" t="s">
         <v>66</v>
       </c>
-      <c r="F69" t="s">
-        <v>162</v>
-      </c>
-      <c r="H69" t="s">
-        <v>164</v>
-      </c>
-      <c r="J69" t="s">
-        <v>166</v>
-      </c>
-      <c r="K69" t="s">
-        <v>167</v>
-      </c>
-      <c r="L69" t="s">
-        <v>168</v>
-      </c>
-      <c r="N69" t="s">
-        <v>170</v>
-      </c>
-      <c r="O69" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D69" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>2</v>
       </c>
@@ -2421,17 +1912,11 @@
       <c r="C70" t="s">
         <v>67</v>
       </c>
-      <c r="E70" t="s">
-        <v>161</v>
-      </c>
-      <c r="F70" t="s">
-        <v>162</v>
-      </c>
-      <c r="L70" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D70" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>3</v>
       </c>
@@ -2441,8 +1926,11 @@
       <c r="C71" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D71" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>3</v>
       </c>
@@ -2452,11 +1940,11 @@
       <c r="C72" t="s">
         <v>69</v>
       </c>
-      <c r="F72" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D72" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>3</v>
       </c>
@@ -2466,14 +1954,11 @@
       <c r="C73" t="s">
         <v>70</v>
       </c>
-      <c r="H73" t="s">
-        <v>164</v>
-      </c>
-      <c r="M73" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D73" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>3</v>
       </c>
@@ -2484,22 +1969,10 @@
         <v>71</v>
       </c>
       <c r="D74" t="s">
-        <v>160</v>
-      </c>
-      <c r="E74" t="s">
-        <v>161</v>
-      </c>
-      <c r="I74" t="s">
-        <v>165</v>
-      </c>
-      <c r="J74" t="s">
-        <v>166</v>
-      </c>
-      <c r="K74" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>6</v>
       </c>
@@ -2509,8 +1982,11 @@
       <c r="C75" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D75" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>6</v>
       </c>
@@ -2520,14 +1996,11 @@
       <c r="C76" t="s">
         <v>73</v>
       </c>
-      <c r="F76" t="s">
-        <v>162</v>
-      </c>
-      <c r="M76" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D76" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>6</v>
       </c>
@@ -2537,17 +2010,11 @@
       <c r="C77" t="s">
         <v>74</v>
       </c>
-      <c r="F77" t="s">
-        <v>162</v>
-      </c>
-      <c r="G77" t="s">
-        <v>163</v>
-      </c>
-      <c r="M77" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D77" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1</v>
       </c>
@@ -2558,37 +2025,10 @@
         <v>75</v>
       </c>
       <c r="D78" t="s">
-        <v>160</v>
-      </c>
-      <c r="F78" t="s">
-        <v>162</v>
-      </c>
-      <c r="G78" t="s">
-        <v>163</v>
-      </c>
-      <c r="H78" t="s">
-        <v>164</v>
-      </c>
-      <c r="I78" t="s">
-        <v>165</v>
-      </c>
-      <c r="J78" t="s">
-        <v>166</v>
-      </c>
-      <c r="K78" t="s">
-        <v>167</v>
-      </c>
-      <c r="L78" t="s">
-        <v>168</v>
-      </c>
-      <c r="M78" t="s">
-        <v>169</v>
-      </c>
-      <c r="N78" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1</v>
       </c>
@@ -2598,11 +2038,11 @@
       <c r="C79" t="s">
         <v>154</v>
       </c>
-      <c r="F79" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D79" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1</v>
       </c>
@@ -2613,37 +2053,10 @@
         <v>77</v>
       </c>
       <c r="D80" t="s">
-        <v>160</v>
-      </c>
-      <c r="E80" t="s">
-        <v>161</v>
-      </c>
-      <c r="F80" t="s">
-        <v>162</v>
-      </c>
-      <c r="G80" t="s">
-        <v>163</v>
-      </c>
-      <c r="H80" t="s">
-        <v>164</v>
-      </c>
-      <c r="I80" t="s">
-        <v>165</v>
-      </c>
-      <c r="J80" t="s">
-        <v>166</v>
-      </c>
-      <c r="L80" t="s">
-        <v>168</v>
-      </c>
-      <c r="N80" t="s">
-        <v>170</v>
-      </c>
-      <c r="O80" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>2</v>
       </c>
@@ -2653,17 +2066,11 @@
       <c r="C81" t="s">
         <v>80</v>
       </c>
-      <c r="F81" t="s">
-        <v>162</v>
-      </c>
-      <c r="G81" t="s">
-        <v>163</v>
-      </c>
-      <c r="H81" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D81" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>2</v>
       </c>
@@ -2673,20 +2080,11 @@
       <c r="C82" t="s">
         <v>81</v>
       </c>
-      <c r="E82" t="s">
-        <v>161</v>
-      </c>
-      <c r="F82" t="s">
-        <v>162</v>
-      </c>
-      <c r="H82" t="s">
-        <v>164</v>
-      </c>
-      <c r="J82" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D82" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>2</v>
       </c>
@@ -2696,17 +2094,11 @@
       <c r="C83" t="s">
         <v>82</v>
       </c>
-      <c r="F83" t="s">
-        <v>162</v>
-      </c>
-      <c r="H83" t="s">
-        <v>164</v>
-      </c>
-      <c r="I83" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D83" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>3</v>
       </c>
@@ -2716,26 +2108,11 @@
       <c r="C84" t="s">
         <v>83</v>
       </c>
-      <c r="E84" t="s">
-        <v>161</v>
-      </c>
-      <c r="F84" t="s">
-        <v>162</v>
-      </c>
-      <c r="G84" t="s">
-        <v>163</v>
-      </c>
-      <c r="H84" t="s">
-        <v>164</v>
-      </c>
-      <c r="I84" t="s">
-        <v>165</v>
-      </c>
-      <c r="L84" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D84" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>3</v>
       </c>
@@ -2746,34 +2123,10 @@
         <v>84</v>
       </c>
       <c r="D85" t="s">
-        <v>160</v>
-      </c>
-      <c r="E85" t="s">
-        <v>161</v>
-      </c>
-      <c r="F85" t="s">
-        <v>162</v>
-      </c>
-      <c r="H85" t="s">
-        <v>164</v>
-      </c>
-      <c r="I85" t="s">
-        <v>165</v>
-      </c>
-      <c r="J85" t="s">
-        <v>166</v>
-      </c>
-      <c r="K85" t="s">
-        <v>167</v>
-      </c>
-      <c r="L85" t="s">
-        <v>168</v>
-      </c>
-      <c r="M85" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>3</v>
       </c>
@@ -2781,10 +2134,13 @@
         <v>86</v>
       </c>
       <c r="C86" t="s">
+        <v>160</v>
+      </c>
+      <c r="D86" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>3</v>
       </c>
@@ -2794,14 +2150,11 @@
       <c r="C87" t="s">
         <v>91</v>
       </c>
-      <c r="F87" t="s">
-        <v>162</v>
-      </c>
-      <c r="G87" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D87" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>3</v>
       </c>
@@ -2812,25 +2165,10 @@
         <v>89</v>
       </c>
       <c r="D88" t="s">
-        <v>160</v>
-      </c>
-      <c r="F88" t="s">
-        <v>162</v>
-      </c>
-      <c r="H88" t="s">
-        <v>164</v>
-      </c>
-      <c r="I88" t="s">
-        <v>165</v>
-      </c>
-      <c r="J88" t="s">
-        <v>166</v>
-      </c>
-      <c r="L88" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>3</v>
       </c>
@@ -2840,14 +2178,11 @@
       <c r="C89" t="s">
         <v>90</v>
       </c>
-      <c r="F89" t="s">
-        <v>162</v>
-      </c>
-      <c r="L89" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D89" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>4</v>
       </c>
@@ -2857,11 +2192,11 @@
       <c r="C90" t="s">
         <v>93</v>
       </c>
-      <c r="H90" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D90" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>5</v>
       </c>
@@ -2871,8 +2206,11 @@
       <c r="C91" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D91" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>5</v>
       </c>
@@ -2882,14 +2220,11 @@
       <c r="C92" t="s">
         <v>95</v>
       </c>
-      <c r="E92" t="s">
-        <v>161</v>
-      </c>
-      <c r="H92" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D92" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>6</v>
       </c>
@@ -2899,8 +2234,11 @@
       <c r="C93" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D93" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>6</v>
       </c>
@@ -2910,8 +2248,11 @@
       <c r="C94" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D94" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>6</v>
       </c>
@@ -2921,14 +2262,11 @@
       <c r="C95" t="s">
         <v>101</v>
       </c>
-      <c r="G95" t="s">
-        <v>163</v>
-      </c>
-      <c r="L95" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D95" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>6</v>
       </c>
@@ -2939,28 +2277,10 @@
         <v>102</v>
       </c>
       <c r="D96" t="s">
-        <v>160</v>
-      </c>
-      <c r="F96" t="s">
-        <v>162</v>
-      </c>
-      <c r="G96" t="s">
-        <v>163</v>
-      </c>
-      <c r="I96" t="s">
-        <v>165</v>
-      </c>
-      <c r="J96" t="s">
-        <v>166</v>
-      </c>
-      <c r="K96" t="s">
-        <v>167</v>
-      </c>
-      <c r="M96" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>6</v>
       </c>
@@ -2970,17 +2290,11 @@
       <c r="C97" t="s">
         <v>103</v>
       </c>
-      <c r="F97" t="s">
-        <v>162</v>
-      </c>
-      <c r="H97" t="s">
-        <v>164</v>
-      </c>
-      <c r="J97" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D97" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>6</v>
       </c>
@@ -2990,53 +2304,44 @@
       <c r="C98" t="s">
         <v>104</v>
       </c>
-      <c r="I98" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D98" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>105</v>
       </c>
       <c r="C99" t="s">
         <v>105</v>
       </c>
-      <c r="E99" t="s">
-        <v>161</v>
-      </c>
-      <c r="F99" t="s">
-        <v>162</v>
-      </c>
-      <c r="H99" t="s">
-        <v>164</v>
-      </c>
-      <c r="J99" t="s">
-        <v>166</v>
-      </c>
-      <c r="N99" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D99" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>107</v>
       </c>
       <c r="C100" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D100" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
         <v>109</v>
       </c>
       <c r="C101" t="s">
         <v>109</v>
       </c>
-      <c r="H101" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D101" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1</v>
       </c>
@@ -3046,8 +2351,11 @@
       <c r="C102" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D102" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>1</v>
       </c>
@@ -3057,17 +2365,11 @@
       <c r="C103" t="s">
         <v>78</v>
       </c>
-      <c r="F103" t="s">
-        <v>162</v>
-      </c>
-      <c r="K103" t="s">
-        <v>167</v>
-      </c>
-      <c r="M103" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D103" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>2</v>
       </c>
@@ -3077,14 +2379,11 @@
       <c r="C104" t="s">
         <v>79</v>
       </c>
-      <c r="F104" t="s">
-        <v>162</v>
-      </c>
-      <c r="I104" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D104" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>3</v>
       </c>
@@ -3094,14 +2393,11 @@
       <c r="C105" t="s">
         <v>85</v>
       </c>
-      <c r="M105" t="s">
-        <v>169</v>
-      </c>
-      <c r="O105" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D105" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>3</v>
       </c>
@@ -3111,8 +2407,11 @@
       <c r="C106" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D106" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>3</v>
       </c>
@@ -3120,30 +2419,24 @@
         <v>88</v>
       </c>
       <c r="C107" t="s">
+        <v>161</v>
+      </c>
+      <c r="D107" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
         <v>106</v>
       </c>
       <c r="C108" t="s">
         <v>106</v>
       </c>
-      <c r="F108" t="s">
-        <v>162</v>
-      </c>
-      <c r="H108" t="s">
-        <v>164</v>
-      </c>
-      <c r="I108" t="s">
-        <v>165</v>
-      </c>
-      <c r="K108" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D108" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>4</v>
       </c>
@@ -3153,20 +2446,11 @@
       <c r="C109" t="s">
         <v>92</v>
       </c>
-      <c r="E109" t="s">
-        <v>161</v>
-      </c>
-      <c r="F109" t="s">
-        <v>162</v>
-      </c>
-      <c r="G109" t="s">
-        <v>163</v>
-      </c>
-      <c r="M109" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D109" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>6</v>
       </c>
@@ -3176,8 +2460,11 @@
       <c r="C110" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D110" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>6</v>
       </c>
@@ -3188,37 +2475,10 @@
         <v>97</v>
       </c>
       <c r="D111" t="s">
-        <v>160</v>
-      </c>
-      <c r="E111" t="s">
-        <v>161</v>
-      </c>
-      <c r="F111" t="s">
-        <v>162</v>
-      </c>
-      <c r="H111" t="s">
-        <v>164</v>
-      </c>
-      <c r="I111" t="s">
-        <v>165</v>
-      </c>
-      <c r="J111" t="s">
-        <v>166</v>
-      </c>
-      <c r="L111" t="s">
-        <v>168</v>
-      </c>
-      <c r="M111" t="s">
-        <v>169</v>
-      </c>
-      <c r="N111" t="s">
-        <v>170</v>
-      </c>
-      <c r="O111" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>5</v>
       </c>
@@ -3229,19 +2489,10 @@
         <v>156</v>
       </c>
       <c r="D112" t="s">
-        <v>160</v>
-      </c>
-      <c r="F112" t="s">
-        <v>162</v>
-      </c>
-      <c r="I112" t="s">
-        <v>165</v>
-      </c>
-      <c r="L112" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>5</v>
       </c>
@@ -3251,29 +2502,11 @@
       <c r="C113" t="s">
         <v>112</v>
       </c>
-      <c r="E113" t="s">
-        <v>161</v>
-      </c>
-      <c r="F113" t="s">
-        <v>162</v>
-      </c>
-      <c r="H113" t="s">
-        <v>164</v>
-      </c>
-      <c r="K113" t="s">
-        <v>167</v>
-      </c>
-      <c r="L113" t="s">
-        <v>168</v>
-      </c>
-      <c r="M113" t="s">
-        <v>169</v>
-      </c>
-      <c r="N113" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D113" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>5</v>
       </c>
@@ -3283,20 +2516,11 @@
       <c r="C114" t="s">
         <v>110</v>
       </c>
-      <c r="F114" t="s">
-        <v>162</v>
-      </c>
-      <c r="H114" t="s">
-        <v>164</v>
-      </c>
-      <c r="I114" t="s">
-        <v>165</v>
-      </c>
-      <c r="M114" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D114" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>6</v>
       </c>
@@ -3307,62 +2531,32 @@
         <v>99</v>
       </c>
       <c r="D115" t="s">
-        <v>160</v>
-      </c>
-      <c r="F115" t="s">
-        <v>162</v>
-      </c>
-      <c r="I115" t="s">
-        <v>165</v>
-      </c>
-      <c r="K115" t="s">
-        <v>167</v>
-      </c>
-      <c r="L115" t="s">
-        <v>168</v>
-      </c>
-      <c r="M115" t="s">
-        <v>169</v>
-      </c>
-      <c r="O115" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
         <v>108</v>
       </c>
       <c r="C116" t="s">
         <v>108</v>
       </c>
-      <c r="M116" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D116" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
         <v>127</v>
       </c>
       <c r="C117" t="s">
         <v>127</v>
       </c>
-      <c r="E117" t="s">
-        <v>161</v>
-      </c>
-      <c r="F117" t="s">
-        <v>162</v>
-      </c>
-      <c r="H117" t="s">
-        <v>164</v>
-      </c>
-      <c r="K117" t="s">
-        <v>167</v>
-      </c>
-      <c r="M117" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D117" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>1</v>
       </c>
@@ -3372,17 +2566,11 @@
       <c r="C118" t="s">
         <v>114</v>
       </c>
-      <c r="F118" t="s">
-        <v>162</v>
-      </c>
-      <c r="H118" t="s">
-        <v>164</v>
-      </c>
-      <c r="M118" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D118" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>5</v>
       </c>
@@ -3392,17 +2580,11 @@
       <c r="C119" t="s">
         <v>115</v>
       </c>
-      <c r="F119" t="s">
-        <v>162</v>
-      </c>
-      <c r="H119" t="s">
-        <v>164</v>
-      </c>
-      <c r="M119" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D119" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>1</v>
       </c>
@@ -3412,8 +2594,11 @@
       <c r="C120" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D120" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>5</v>
       </c>
@@ -3423,11 +2608,11 @@
       <c r="C121" t="s">
         <v>117</v>
       </c>
-      <c r="M121" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D121" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>3</v>
       </c>
@@ -3438,13 +2623,10 @@
         <v>118</v>
       </c>
       <c r="D122" t="s">
-        <v>160</v>
-      </c>
-      <c r="I122" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>6</v>
       </c>
@@ -3454,8 +2636,11 @@
       <c r="C123" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D123" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>6</v>
       </c>
@@ -3465,11 +2650,11 @@
       <c r="C124" t="s">
         <v>120</v>
       </c>
-      <c r="F124" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D124" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>1</v>
       </c>
@@ -3479,17 +2664,11 @@
       <c r="C125" t="s">
         <v>121</v>
       </c>
-      <c r="E125" t="s">
-        <v>161</v>
-      </c>
-      <c r="J125" t="s">
-        <v>166</v>
-      </c>
-      <c r="M125" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D125" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>1</v>
       </c>
@@ -3499,11 +2678,11 @@
       <c r="C126" t="s">
         <v>122</v>
       </c>
-      <c r="G126" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D126" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>3</v>
       </c>
@@ -3513,11 +2692,11 @@
       <c r="C127" t="s">
         <v>123</v>
       </c>
-      <c r="M127" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D127" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>3</v>
       </c>
@@ -3527,14 +2706,11 @@
       <c r="C128" t="s">
         <v>124</v>
       </c>
-      <c r="J128" t="s">
-        <v>166</v>
-      </c>
-      <c r="L128" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D128" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>5</v>
       </c>
@@ -3544,11 +2720,11 @@
       <c r="C129" t="s">
         <v>125</v>
       </c>
-      <c r="F129" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D129" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>6</v>
       </c>
@@ -3559,25 +2735,10 @@
         <v>126</v>
       </c>
       <c r="D130" t="s">
-        <v>160</v>
-      </c>
-      <c r="E130" t="s">
-        <v>161</v>
-      </c>
-      <c r="G130" t="s">
-        <v>163</v>
-      </c>
-      <c r="I130" t="s">
-        <v>165</v>
-      </c>
-      <c r="L130" t="s">
-        <v>168</v>
-      </c>
-      <c r="M130" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>128</v>
       </c>
@@ -3585,98 +2746,65 @@
         <v>128</v>
       </c>
       <c r="D131" t="s">
-        <v>160</v>
-      </c>
-      <c r="G131" t="s">
-        <v>163</v>
-      </c>
-      <c r="H131" t="s">
-        <v>164</v>
-      </c>
-      <c r="I131" t="s">
-        <v>165</v>
-      </c>
-      <c r="J131" t="s">
-        <v>166</v>
-      </c>
-      <c r="L131" t="s">
-        <v>168</v>
-      </c>
-      <c r="M131" t="s">
-        <v>169</v>
-      </c>
-      <c r="N131" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>129</v>
       </c>
       <c r="C132" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D132" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>130</v>
       </c>
       <c r="C133" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D133" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>131</v>
       </c>
       <c r="C134" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D134" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>132</v>
       </c>
       <c r="C135" t="s">
         <v>132</v>
       </c>
-      <c r="O135" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D135" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>133</v>
       </c>
       <c r="C136" t="s">
         <v>133</v>
       </c>
-      <c r="E136" t="s">
-        <v>161</v>
-      </c>
-      <c r="F136" t="s">
-        <v>162</v>
-      </c>
-      <c r="G136" t="s">
-        <v>163</v>
-      </c>
-      <c r="H136" t="s">
-        <v>164</v>
-      </c>
-      <c r="J136" t="s">
-        <v>166</v>
-      </c>
-      <c r="M136" t="s">
-        <v>169</v>
-      </c>
-      <c r="N136" t="s">
-        <v>170</v>
-      </c>
-      <c r="O136" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D136" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B137" t="s">
         <v>134</v>
       </c>
@@ -3684,59 +2812,32 @@
         <v>134</v>
       </c>
       <c r="D137" t="s">
-        <v>160</v>
-      </c>
-      <c r="E137" t="s">
-        <v>161</v>
-      </c>
-      <c r="F137" t="s">
-        <v>162</v>
-      </c>
-      <c r="G137" t="s">
-        <v>163</v>
-      </c>
-      <c r="H137" t="s">
-        <v>164</v>
-      </c>
-      <c r="I137" t="s">
-        <v>165</v>
-      </c>
-      <c r="J137" t="s">
-        <v>166</v>
-      </c>
-      <c r="L137" t="s">
-        <v>168</v>
-      </c>
-      <c r="M137" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B138" t="s">
         <v>135</v>
       </c>
       <c r="C138" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D138" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
         <v>136</v>
       </c>
       <c r="C139" t="s">
         <v>136</v>
       </c>
-      <c r="E139" t="s">
-        <v>161</v>
-      </c>
-      <c r="G139" t="s">
-        <v>163</v>
-      </c>
-      <c r="J139" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D139" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>1</v>
       </c>
@@ -3746,8 +2847,11 @@
       <c r="C140" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D140" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>1</v>
       </c>
@@ -3755,10 +2859,13 @@
         <v>148</v>
       </c>
       <c r="C141" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+      <c r="D141" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>2</v>
       </c>
@@ -3766,10 +2873,13 @@
         <v>145</v>
       </c>
       <c r="C142" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="D142" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>3</v>
       </c>
@@ -3779,8 +2889,11 @@
       <c r="C143" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D143" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>3</v>
       </c>
@@ -3788,10 +2901,13 @@
         <v>146</v>
       </c>
       <c r="C144" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+      <c r="D144" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>5</v>
       </c>
@@ -3801,8 +2917,11 @@
       <c r="C145" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D145" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>6</v>
       </c>
@@ -3812,8 +2931,11 @@
       <c r="C146" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D146" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>6</v>
       </c>
@@ -3823,8 +2945,11 @@
       <c r="C147" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D147" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>6</v>
       </c>
@@ -3834,8 +2959,11 @@
       <c r="C148" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D148" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>6</v>
       </c>
@@ -3845,21 +2973,30 @@
       <c r="C149" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D149" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
         <v>147</v>
       </c>
       <c r="C150" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+      <c r="D150" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
         <v>142</v>
       </c>
       <c r="C151" t="s">
         <v>159</v>
+      </c>
+      <c r="D151" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
